--- a/ZonasEscolares/excels/PIURA-HUANCABAMBA-HUANCABAMBA.xlsx
+++ b/ZonasEscolares/excels/PIURA-HUANCABAMBA-HUANCABAMBA.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/PIURA-HUANCABAMBA-HUANCABAMBA.xlsx
+++ b/ZonasEscolares/excels/PIURA-HUANCABAMBA-HUANCABAMBA.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,66 +413,66 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L20"/>
+  <dimension ref="A1:L30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>14408 VIRGEN DE LAS MERCEDES</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-5.242442</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-79.449822</v>
-      </c>
-      <c r="I2" t="n">
-        <v>749</v>
-      </c>
-      <c r="J2" t="n">
-        <v>33</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-5.242442</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-79.449822</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>749</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>14409 NUESTRA SEÑORA DEL CARMEN</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-5.238423</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-79.451645</v>
-      </c>
-      <c r="I3" t="n">
-        <v>858</v>
-      </c>
-      <c r="J3" t="n">
-        <v>40</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-5.238423</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-79.451645</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>858</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>14420</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-5.137728</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-79.525256</v>
-      </c>
-      <c r="I4" t="n">
-        <v>201</v>
-      </c>
-      <c r="J4" t="n">
-        <v>17</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-5.137728</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-79.525256</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>14426 CARLOS AUGUSTO SALAVERRY</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-5.263912</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-79.486784</v>
-      </c>
-      <c r="I5" t="n">
-        <v>243</v>
-      </c>
-      <c r="J5" t="n">
-        <v>16</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-5.263912</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-79.486784</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>14429 RICARDO HUMBERTO RAMOS PLATA</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-5.195498</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-79.53180399999999</v>
-      </c>
-      <c r="I6" t="n">
-        <v>251</v>
-      </c>
-      <c r="J6" t="n">
-        <v>19</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-5.195498</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-79.531804</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>14438 MARIA AUXILIADORA</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-5.255381</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-79.53104500000001</v>
-      </c>
-      <c r="I7" t="n">
-        <v>212</v>
-      </c>
-      <c r="J7" t="n">
-        <v>18</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-5.255381</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-79.531045</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>AGROPECUARIO 13</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-5.23515</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-79.45399</v>
-      </c>
-      <c r="I8" t="n">
-        <v>403</v>
-      </c>
-      <c r="J8" t="n">
-        <v>31</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-5.23515</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-79.45399</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>SAN FRANCISCO DE ASIS</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-5.24229</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-79.450526</v>
-      </c>
-      <c r="I9" t="n">
-        <v>510</v>
-      </c>
-      <c r="J9" t="n">
-        <v>37</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-5.24229</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-79.450526</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>510</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>EMILIO ESPINOZA</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-5.3759</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-79.60429999999999</v>
-      </c>
-      <c r="I10" t="n">
-        <v>254</v>
-      </c>
-      <c r="J10" t="n">
-        <v>22</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-5.3759</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-79.6043</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>JORGE ALFREDO BASADRE GROHMANN</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-5.85709</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-79.65159</v>
-      </c>
-      <c r="I11" t="n">
-        <v>104</v>
-      </c>
-      <c r="J11" t="n">
-        <v>12</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-5.85709</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-79.65159</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>SANTA ANA</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-5.567771</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-79.52535899999999</v>
-      </c>
-      <c r="I12" t="n">
-        <v>635</v>
-      </c>
-      <c r="J12" t="n">
-        <v>35</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-5.567771</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-79.525359</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>635</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>SAN MARTIN</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-5.44327</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-79.55774</v>
-      </c>
-      <c r="I13" t="n">
-        <v>218</v>
-      </c>
-      <c r="J13" t="n">
-        <v>13</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-5.44327</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-79.55774</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>379</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-5.4694</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-79.35132900000001</v>
-      </c>
-      <c r="I14" t="n">
-        <v>29</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-5.4694</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-79.351329</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>VIRGEN DE LAS MERCEDES</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-5.469073</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-79.350753</v>
-      </c>
-      <c r="I15" t="n">
-        <v>59</v>
-      </c>
-      <c r="J15" t="n">
-        <v>5</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-5.469073</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-79.350753</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>14537 AUGUSTO SALAZAR BONDY</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-5.31567</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-79.46335999999999</v>
-      </c>
-      <c r="I16" t="n">
-        <v>203</v>
-      </c>
-      <c r="J16" t="n">
-        <v>18</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-5.31567</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-79.46336</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>LUIS ANTONIO PAREDES MACEDA</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-5.34435</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-79.47581</v>
-      </c>
-      <c r="I17" t="n">
-        <v>220</v>
-      </c>
-      <c r="J17" t="n">
-        <v>18</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-5.34435</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-79.47581</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>PEDRO POTENCIANO CHOQUEHUANCA</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-5.338374</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-79.493227</v>
-      </c>
-      <c r="I18" t="n">
-        <v>229</v>
-      </c>
-      <c r="J18" t="n">
-        <v>20</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-5.338374</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-79.493227</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-5.338363</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-79.429483</v>
-      </c>
-      <c r="I19" t="n">
-        <v>286</v>
-      </c>
-      <c r="J19" t="n">
-        <v>27</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-5.338363</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-79.429483</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,22 +1625,652 @@
           <t>20486</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-5.355096</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-79.45769900000001</v>
-      </c>
-      <c r="I20" t="n">
-        <v>345</v>
-      </c>
-      <c r="J20" t="n">
-        <v>21</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-5.355096</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-79.457699</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>345</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>200301</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>HUANCABAMBA</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>HUANCABAMBA</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>423783</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>204 GENARA LITUMA PORTOCARRERO</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-5.23933</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-79.44933</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>200301</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>HUANCABAMBA</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>HUANCABAMBA</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>423962</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>14416 JESUS MI AMIGO</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-5.2543</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-79.45071</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>200301</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>HUANCABAMBA</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>HUANCABAMBA</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>423981</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>14418 NUESTRA SEÑORA DE LOURDES</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-5.24302</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-79.452978</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>200301</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>HUANCABAMBA</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>HUANCABAMBA</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>424283</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>14991 THOMAS ALVA EDISON</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-5.23299</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-79.459813</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>200301</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>HUANCABAMBA</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>HUANCABAMBA</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>424495</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>NUESTRA.SEÑORA.DEL PERPETUO SOCORRO</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-5.17548</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-79.45115</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>200301</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>HUANCABAMBA</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>HUANCABAMBA</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>424513</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>MARIA INMACULADA</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-5.237841</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-79.450465</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>473</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>200301</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>HUANCABAMBA</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>HUANCABAMBA</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>425796</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>ALMIRANTE MIGUEL GRAU Y SEMINARIO</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-5.149033</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-79.429379</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>200301</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>HUANCABAMBA</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>HUANCABAMBA</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>428747</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>14523</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-5.290449</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-79.423685</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>200301</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>HUANCABAMBA</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>HUANCABAMBA</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>428931</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>SAN JOSE</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-5.29148</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-79.423097</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>200301</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>HUANCABAMBA</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>HUANCABAMBA</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>428945</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>VIRGEN DE LA ASUNCION</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-5.315991</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-79.407195</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>291</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
         <is>
           <t>No</t>
         </is>

--- a/ZonasEscolares/excels/PIURA-HUANCABAMBA-HUANCABAMBA.xlsx
+++ b/ZonasEscolares/excels/PIURA-HUANCABAMBA-HUANCABAMBA.xlsx
@@ -501,37 +501,37 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>423882</t>
+          <t>426913</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>14408 VIRGEN DE LAS MERCEDES</t>
+          <t>JORGE ALFREDO BASADRE GROHMANN</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-5.242442</t>
+          <t>-5.85709</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-79.449822</t>
+          <t>-79.65159</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>749</t>
+          <t>104</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>423896</t>
+          <t>428281</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>14409 NUESTRA SEÑORA DEL CARMEN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-5.238423</t>
+          <t>-5.44327</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-79.451645</t>
+          <t>-79.55774</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>858</t>
+          <t>218</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>424004</t>
+          <t>424037</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>14420</t>
+          <t>14426 CARLOS AUGUSTO SALAVERRY</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-5.137728</t>
+          <t>-5.263912</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-79.525256</t>
+          <t>-79.486784</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>243</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>424037</t>
+          <t>424004</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>14426 CARLOS AUGUSTO SALAVERRY</t>
+          <t>14420</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-5.263912</t>
+          <t>-5.137728</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-79.486784</t>
+          <t>-79.525256</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>201</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>424061</t>
+          <t>424141</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>14429 RICARDO HUMBERTO RAMOS PLATA</t>
+          <t>14438 MARIA AUXILIADORA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-5.195498</t>
+          <t>-5.255381</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-79.531804</t>
+          <t>-79.531045</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>212</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,27 +811,27 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>424141</t>
+          <t>429025</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>14438 MARIA AUXILIADORA</t>
+          <t>14537 AUGUSTO SALAZAR BONDY</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-5.255381</t>
+          <t>-5.31567</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-79.531045</t>
+          <t>-79.46336</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>203</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>424476</t>
+          <t>429030</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AGROPECUARIO 13</t>
+          <t>LUIS ANTONIO PAREDES MACEDA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-5.23515</t>
+          <t>-5.34435</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-79.45399</t>
+          <t>-79.47581</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>220</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>424527</t>
+          <t>424061</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SAN FRANCISCO DE ASIS</t>
+          <t>14429 RICARDO HUMBERTO RAMOS PLATA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-5.24229</t>
+          <t>-5.195498</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-79.450526</t>
+          <t>-79.531804</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>251</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,37 +997,37 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>425008</t>
+          <t>428634</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>EMILIO ESPINOZA</t>
+          <t>379</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-5.3759</t>
+          <t>-5.4694</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-79.6043</t>
+          <t>-79.351329</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>29</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1059,37 +1059,37 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>426913</t>
+          <t>429209</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>JORGE ALFREDO BASADRE GROHMANN</t>
+          <t>PEDRO POTENCIANO CHOQUEHUANCA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-5.85709</t>
+          <t>-5.338374</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-79.65159</t>
+          <t>-79.493227</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>229</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>427724</t>
+          <t>771602</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>SANTA ANA</t>
+          <t>20486</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-5.567771</t>
+          <t>-5.355096</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-79.525359</t>
+          <t>-79.457699</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>345</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>428281</t>
+          <t>425008</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SAN MARTIN</t>
+          <t>EMILIO ESPINOZA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-5.44327</t>
+          <t>-5.3759</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-79.55774</t>
+          <t>-79.6043</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>254</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,37 +1245,37 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>428634</t>
+          <t>429214</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-5.4694</t>
+          <t>-5.338363</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-79.351329</t>
+          <t>-79.429483</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>286</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1307,37 +1307,37 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>428728</t>
+          <t>424476</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>VIRGEN DE LAS MERCEDES</t>
+          <t>AGROPECUARIO 13</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-5.469073</t>
+          <t>-5.23515</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-79.350753</t>
+          <t>-79.45399</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>403</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>429025</t>
+          <t>423882</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>14537 AUGUSTO SALAZAR BONDY</t>
+          <t>14408 VIRGEN DE LAS MERCEDES</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-5.31567</t>
+          <t>-5.242442</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-79.46336</t>
+          <t>-79.449822</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>749</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>429030</t>
+          <t>427724</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>LUIS ANTONIO PAREDES MACEDA</t>
+          <t>SANTA ANA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-5.34435</t>
+          <t>-5.567771</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-79.47581</t>
+          <t>-79.525359</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>635</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>429209</t>
+          <t>424527</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>PEDRO POTENCIANO CHOQUEHUANCA</t>
+          <t>SAN FRANCISCO DE ASIS</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-5.338374</t>
+          <t>-5.24229</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-79.493227</t>
+          <t>-79.450526</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>510</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>429214</t>
+          <t>423896</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>SAN JUAN BAUTISTA</t>
+          <t>14409 NUESTRA SEÑORA DEL CARMEN</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-5.338363</t>
+          <t>-5.238423</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-79.429483</t>
+          <t>-79.451645</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>858</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,37 +1617,37 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>771602</t>
+          <t>428728</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>20486</t>
+          <t>VIRGEN DE LAS MERCEDES</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-5.355096</t>
+          <t>-5.469073</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-79.457699</t>
+          <t>-79.350753</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>59</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>56</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">

--- a/ZonasEscolares/excels/PIURA-HUANCABAMBA-HUANCABAMBA.xlsx
+++ b/ZonasEscolares/excels/PIURA-HUANCABAMBA-HUANCABAMBA.xlsx
@@ -501,37 +501,37 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>426913</t>
+          <t>771602</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>JORGE ALFREDO BASADRE GROHMANN</t>
+          <t>20486</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-5.85709</t>
+          <t>345</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-79.65159</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>-5.355096</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-79.457699</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>428281</t>
+          <t>429214</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>SAN MARTIN</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-5.44327</t>
+          <t>286</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-79.55774</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>-5.338363</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-79.429483</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>424037</t>
+          <t>429209</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>14426 CARLOS AUGUSTO SALAVERRY</t>
+          <t>PEDRO POTENCIANO CHOQUEHUANCA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-5.263912</t>
+          <t>229</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-79.486784</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>-5.338374</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-79.493227</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>424004</t>
+          <t>429030</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>14420</t>
+          <t>LUIS ANTONIO PAREDES MACEDA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-5.137728</t>
+          <t>220</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-79.525256</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>-5.34435</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-79.47581</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>424141</t>
+          <t>429025</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>14438 MARIA AUXILIADORA</t>
+          <t>14537 AUGUSTO SALAZAR BONDY</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-5.255381</t>
+          <t>203</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-79.531045</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>-5.31567</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-79.46336</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>429025</t>
+          <t>428945</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>14537 AUGUSTO SALAZAR BONDY</t>
+          <t>VIRGEN DE LA ASUNCION</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-5.31567</t>
+          <t>291</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-79.46336</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>-5.315991</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-79.407195</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>429030</t>
+          <t>428931</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>LUIS ANTONIO PAREDES MACEDA</t>
+          <t>SAN JOSE</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-5.34435</t>
+          <t>78</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-79.47581</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>-5.29148</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-79.423097</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>424061</t>
+          <t>428747</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>14429 RICARDO HUMBERTO RAMOS PLATA</t>
+          <t>14523</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-5.195498</t>
+          <t>90</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-79.531804</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>-5.290449</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-79.423685</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>428634</t>
+          <t>428728</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>VIRGEN DE LAS MERCEDES</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-5.4694</t>
+          <t>59</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-79.351329</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-5.469073</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>-79.350753</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,37 +1059,37 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>429209</t>
+          <t>428634</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>PEDRO POTENCIANO CHOQUEHUANCA</t>
+          <t>379</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-5.338374</t>
+          <t>29</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-79.493227</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>-5.4694</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-79.351329</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>771602</t>
+          <t>428281</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>20486</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-5.355096</t>
+          <t>218</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-79.457699</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>-5.44327</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-79.55774</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>425008</t>
+          <t>427724</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>EMILIO ESPINOZA</t>
+          <t>SANTA ANA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-5.3759</t>
+          <t>635</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-79.6043</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>-5.567771</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-79.525359</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,37 +1245,37 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>429214</t>
+          <t>426913</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SAN JUAN BAUTISTA</t>
+          <t>JORGE ALFREDO BASADRE GROHMANN</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-5.338363</t>
+          <t>104</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-79.429483</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>-5.85709</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-79.65159</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>424476</t>
+          <t>425796</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>AGROPECUARIO 13</t>
+          <t>ALMIRANTE MIGUEL GRAU Y SEMINARIO</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-5.23515</t>
+          <t>142</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-79.45399</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>-5.149033</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-79.429379</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>423882</t>
+          <t>425008</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>14408 VIRGEN DE LAS MERCEDES</t>
+          <t>EMILIO ESPINOZA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-5.242442</t>
+          <t>254</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-79.449822</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>749</t>
+          <t>-5.3759</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>-79.6043</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>427724</t>
+          <t>424527</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>SANTA ANA</t>
+          <t>SAN FRANCISCO DE ASIS</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-5.567771</t>
+          <t>510</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-79.525359</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>-5.24229</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>-79.450526</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>424527</t>
+          <t>424513</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SAN FRANCISCO DE ASIS</t>
+          <t>MARIA INMACULADA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-5.24229</t>
+          <t>473</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-79.450526</t>
+          <t>56</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>-5.237841</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>-79.450465</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>423896</t>
+          <t>424495</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>14409 NUESTRA SEÑORA DEL CARMEN</t>
+          <t>NUESTRA.SEÑORA.DEL PERPETUO SOCORRO</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-5.238423</t>
+          <t>75</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-79.451645</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>858</t>
+          <t>-5.17548</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>-79.45115</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,37 +1617,37 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>428728</t>
+          <t>424476</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>VIRGEN DE LAS MERCEDES</t>
+          <t>AGROPECUARIO 13</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-5.469073</t>
+          <t>403</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-79.350753</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>-5.23515</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>-79.45399</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>423783</t>
+          <t>424283</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>204 GENARA LITUMA PORTOCARRERO</t>
+          <t>14991 THOMAS ALVA EDISON</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-5.23933</t>
+          <t>112</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-79.44933</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>-5.23299</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-79.459813</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>423962</t>
+          <t>424141</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>14416 JESUS MI AMIGO</t>
+          <t>14438 MARIA AUXILIADORA</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-5.2543</t>
+          <t>212</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-79.45071</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>-5.255381</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>-79.531045</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>423981</t>
+          <t>424061</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>14418 NUESTRA SEÑORA DE LOURDES</t>
+          <t>14429 RICARDO HUMBERTO RAMOS PLATA</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-5.24302</t>
+          <t>251</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-79.452978</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>-5.195498</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-79.531804</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>424283</t>
+          <t>424037</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>14991 THOMAS ALVA EDISON</t>
+          <t>14426 CARLOS AUGUSTO SALAVERRY</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-5.23299</t>
+          <t>243</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-79.459813</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>-5.263912</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-79.486784</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>424495</t>
+          <t>424004</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>NUESTRA.SEÑORA.DEL PERPETUO SOCORRO</t>
+          <t>14420</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-5.17548</t>
+          <t>201</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-79.45115</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>-5.137728</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-79.525256</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>424513</t>
+          <t>423981</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>MARIA INMACULADA</t>
+          <t>14418 NUESTRA SEÑORA DE LOURDES</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-5.237841</t>
+          <t>44</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-79.450465</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>473</t>
+          <t>-5.24302</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>-79.452978</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>425796</t>
+          <t>423962</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>ALMIRANTE MIGUEL GRAU Y SEMINARIO</t>
+          <t>14416 JESUS MI AMIGO</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-5.149033</t>
+          <t>65</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-79.429379</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>-5.2543</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-79.45071</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>428747</t>
+          <t>423896</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>14523</t>
+          <t>14409 NUESTRA SEÑORA DEL CARMEN</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-5.290449</t>
+          <t>858</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-79.423685</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>-5.238423</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>-79.451645</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>428931</t>
+          <t>423882</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>SAN JOSE</t>
+          <t>14408 VIRGEN DE LAS MERCEDES</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-5.29148</t>
+          <t>749</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-79.423097</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>-5.242442</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-79.449822</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>428945</t>
+          <t>423783</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>VIRGEN DE LA ASUNCION</t>
+          <t>204 GENARA LITUMA PORTOCARRERO</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-5.315991</t>
+          <t>210</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-79.407195</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>-5.23933</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-79.44933</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">

--- a/ZonasEscolares/excels/PIURA-HUANCABAMBA-HUANCABAMBA.xlsx
+++ b/ZonasEscolares/excels/PIURA-HUANCABAMBA-HUANCABAMBA.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
